--- a/Encollect_Web_DBS_P3/Cypress/downloads/Bulktrail.xlsx
+++ b/Encollect_Web_DBS_P3/Cypress/downloads/Bulktrail.xlsx
@@ -1,24 +1,35 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\A Product Base\Entiger_Master_Web_App\src\assets\templates\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Deploy and Backup\DBS\19122025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6631D02E-2733-42DA-9754-4789078AC5D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56233E06-C520-4C4F-8130-AE72F4B16E2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -33,22 +44,22 @@
     <t>Agent ENCollect Code</t>
   </si>
   <si>
-    <t>Action Code</t>
-  </si>
-  <si>
-    <t>ResultCode</t>
+    <t>RightPartyContact</t>
+  </si>
+  <si>
+    <t>Next Action Date</t>
+  </si>
+  <si>
+    <t>PTP Amount ( only if action code is PTP)</t>
   </si>
   <si>
     <t>NextActionCode</t>
   </si>
   <si>
-    <t>Next Action Date</t>
-  </si>
-  <si>
     <t>Remarks</t>
   </si>
   <si>
-    <t>PTP Amount ( only if action code is PTP)</t>
+    <t>New contact number</t>
   </si>
   <si>
     <t>New Area</t>
@@ -57,12 +68,6 @@
     <t>New Address</t>
   </si>
   <si>
-    <t>New contact number</t>
-  </si>
-  <si>
-    <t>RightPartyContact</t>
-  </si>
-  <si>
     <t>NewEmailID</t>
   </si>
   <si>
@@ -70,6 +75,12 @@
   </si>
   <si>
     <t>PickupAddress</t>
+  </si>
+  <si>
+    <t>Disposition Code Group</t>
+  </si>
+  <si>
+    <t>Disposition Code</t>
   </si>
 </sst>
 </file>
@@ -116,12 +127,10 @@
   </cellStyleXfs>
   <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -141,9 +150,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -181,7 +190,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -287,7 +296,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -429,7 +438,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -437,27 +446,26 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O2"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:O9"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="19.54296875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="20.54296875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="20.54296875" customWidth="1"/>
-    <col min="4" max="4" width="11.7265625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.1796875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.1796875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="36.7265625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.7265625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.54296875" customWidth="1"/>
-    <col min="10" max="10" width="19.7265625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="9.7265625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12.7265625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="23" style="2" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="12.453125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.1796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="22.9296875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.59765625" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="20.59765625" customWidth="1"/>
+    <col min="5" max="5" width="18.19921875" customWidth="1"/>
+    <col min="6" max="6" width="16.1328125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="36.73046875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.73046875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.59765625" customWidth="1"/>
+    <col min="10" max="10" width="19.73046875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.73046875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.73046875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="23" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12.3984375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.1328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -465,28 +473,28 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="E1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F1" t="s">
         <v>3</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
+        <v>4</v>
+      </c>
+      <c r="H1" t="s">
         <v>5</v>
-      </c>
-      <c r="G1" t="s">
-        <v>7</v>
-      </c>
-      <c r="H1" t="s">
-        <v>4</v>
       </c>
       <c r="I1" t="s">
         <v>6</v>
       </c>
       <c r="J1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="K1" t="s">
         <v>8</v>
@@ -494,23 +502,48 @@
       <c r="L1" t="s">
         <v>9</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="M1" t="s">
+        <v>10</v>
+      </c>
+      <c r="N1" t="s">
+        <v>11</v>
+      </c>
+      <c r="O1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" t="s">
-        <v>13</v>
-      </c>
-      <c r="O1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A2"/>
-      <c r="F2" s="4"/>
-      <c r="M2" s="3"/>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A2" s="4"/>
+      <c r="F2" s="3"/>
+      <c r="M2" s="2"/>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A3" s="3"/>
+      <c r="F3" s="3"/>
+      <c r="M3" s="2"/>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A4" s="3"/>
+      <c r="F4" s="3"/>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A5" s="3"/>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A6" s="3"/>
+      <c r="F6" s="3"/>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A7" s="3"/>
+      <c r="F7" s="3"/>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A8" s="3"/>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A9" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>